--- a/JANUARY 2026/BAR JANUARY 2026.xlsx
+++ b/JANUARY 2026/BAR JANUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16600" windowHeight="17020" firstSheet="7" activeTab="7"/>
+    <workbookView windowWidth="17160" windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -45,10 +45,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1553,7 +1549,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2436,29 +2432,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="28" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="28" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4473,7 +4451,7 @@
     <col min="3" max="3" width="9.140625" style="251"/>
     <col min="4" max="4" width="15.859375" style="250" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" style="250" customWidth="1"/>
-    <col min="6" max="6" width="25.8671875" style="250" customWidth="1"/>
+    <col min="6" max="6" width="14.1875" style="250" customWidth="1"/>
     <col min="7" max="7" width="21.8125" style="250" customWidth="1"/>
     <col min="8" max="8" width="13.140625" style="250"/>
     <col min="9" max="16384" width="9.140625" style="250"/>
@@ -7255,246 +7233,246 @@
       <c r="G150" s="291"/>
     </row>
     <row r="151" s="250" customFormat="1" spans="1:7">
-      <c r="A151" s="294">
+      <c r="A151" s="281">
         <v>46038</v>
       </c>
-      <c r="B151" s="295" t="s">
+      <c r="B151" s="294" t="s">
         <v>30</v>
       </c>
       <c r="C151" s="283">
         <v>6</v>
       </c>
-      <c r="D151" s="296">
+      <c r="D151" s="295">
         <v>10000</v>
       </c>
       <c r="E151" s="265">
         <f t="shared" si="7"/>
         <v>60000</v>
       </c>
-      <c r="F151" s="299">
+      <c r="F151" s="288">
         <f>SUM(E151:E163)</f>
         <v>738000</v>
       </c>
-      <c r="G151" s="299" t="s">
+      <c r="G151" s="288" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="152" s="250" customFormat="1" spans="1:7">
-      <c r="A152" s="297"/>
-      <c r="B152" s="295" t="s">
+      <c r="A152" s="284"/>
+      <c r="B152" s="294" t="s">
         <v>45</v>
       </c>
       <c r="C152" s="283">
         <v>5</v>
       </c>
-      <c r="D152" s="296">
+      <c r="D152" s="295">
         <v>20000</v>
       </c>
       <c r="E152" s="265">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="F152" s="300"/>
-      <c r="G152" s="300"/>
+      <c r="F152" s="289"/>
+      <c r="G152" s="289"/>
     </row>
     <row r="153" s="250" customFormat="1" spans="1:7">
-      <c r="A153" s="297"/>
-      <c r="B153" s="295" t="s">
+      <c r="A153" s="284"/>
+      <c r="B153" s="294" t="s">
         <v>7</v>
       </c>
       <c r="C153" s="283">
         <v>3</v>
       </c>
-      <c r="D153" s="296">
+      <c r="D153" s="295">
         <v>70000</v>
       </c>
       <c r="E153" s="265">
         <f t="shared" si="7"/>
         <v>210000</v>
       </c>
-      <c r="F153" s="300"/>
-      <c r="G153" s="300"/>
+      <c r="F153" s="289"/>
+      <c r="G153" s="289"/>
     </row>
     <row r="154" s="250" customFormat="1" spans="1:7">
-      <c r="A154" s="297"/>
-      <c r="B154" s="295" t="s">
+      <c r="A154" s="284"/>
+      <c r="B154" s="294" t="s">
         <v>37</v>
       </c>
       <c r="C154" s="283">
         <v>1</v>
       </c>
-      <c r="D154" s="296">
+      <c r="D154" s="295">
         <v>15000</v>
       </c>
       <c r="E154" s="265">
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F154" s="300"/>
-      <c r="G154" s="300"/>
+      <c r="F154" s="289"/>
+      <c r="G154" s="289"/>
     </row>
     <row r="155" s="250" customFormat="1" spans="1:7">
-      <c r="A155" s="297"/>
-      <c r="B155" s="295" t="s">
+      <c r="A155" s="284"/>
+      <c r="B155" s="294" t="s">
         <v>40</v>
       </c>
       <c r="C155" s="283">
         <v>1</v>
       </c>
-      <c r="D155" s="296">
+      <c r="D155" s="295">
         <v>48000</v>
       </c>
       <c r="E155" s="265">
         <f t="shared" si="7"/>
         <v>48000</v>
       </c>
-      <c r="F155" s="300"/>
-      <c r="G155" s="300"/>
+      <c r="F155" s="289"/>
+      <c r="G155" s="289"/>
     </row>
     <row r="156" s="250" customFormat="1" spans="1:7">
-      <c r="A156" s="297"/>
-      <c r="B156" s="295" t="s">
+      <c r="A156" s="284"/>
+      <c r="B156" s="294" t="s">
         <v>20</v>
       </c>
       <c r="C156" s="283">
         <v>1.1</v>
       </c>
-      <c r="D156" s="296">
+      <c r="D156" s="295">
         <v>40000</v>
       </c>
       <c r="E156" s="265">
         <f t="shared" si="7"/>
         <v>44000</v>
       </c>
-      <c r="F156" s="300"/>
-      <c r="G156" s="300"/>
+      <c r="F156" s="289"/>
+      <c r="G156" s="289"/>
     </row>
     <row r="157" s="250" customFormat="1" spans="1:7">
-      <c r="A157" s="297"/>
-      <c r="B157" s="295" t="s">
+      <c r="A157" s="284"/>
+      <c r="B157" s="294" t="s">
         <v>17</v>
       </c>
       <c r="C157" s="283">
         <v>3.225</v>
       </c>
-      <c r="D157" s="296">
+      <c r="D157" s="295">
         <v>15000</v>
       </c>
       <c r="E157" s="265">
         <v>48000</v>
       </c>
-      <c r="F157" s="300"/>
-      <c r="G157" s="300"/>
+      <c r="F157" s="289"/>
+      <c r="G157" s="289"/>
     </row>
     <row r="158" s="250" customFormat="1" spans="1:7">
-      <c r="A158" s="297"/>
-      <c r="B158" s="295" t="s">
+      <c r="A158" s="284"/>
+      <c r="B158" s="294" t="s">
         <v>47</v>
       </c>
       <c r="C158" s="283">
         <v>1</v>
       </c>
-      <c r="D158" s="296">
+      <c r="D158" s="295">
         <v>34000</v>
       </c>
       <c r="E158" s="265">
         <f t="shared" ref="E158:E163" si="8">D158*C158</f>
         <v>34000</v>
       </c>
-      <c r="F158" s="300"/>
-      <c r="G158" s="300"/>
+      <c r="F158" s="289"/>
+      <c r="G158" s="289"/>
     </row>
     <row r="159" s="250" customFormat="1" spans="1:8">
-      <c r="A159" s="297"/>
-      <c r="B159" s="295" t="s">
+      <c r="A159" s="284"/>
+      <c r="B159" s="294" t="s">
         <v>32</v>
       </c>
       <c r="C159" s="283">
         <v>0.3</v>
       </c>
-      <c r="D159" s="296">
+      <c r="D159" s="295">
         <v>20000</v>
       </c>
       <c r="E159" s="265">
         <f t="shared" si="8"/>
         <v>6000</v>
       </c>
-      <c r="F159" s="300"/>
-      <c r="G159" s="300"/>
+      <c r="F159" s="289"/>
+      <c r="G159" s="289"/>
       <c r="H159" s="270"/>
     </row>
     <row r="160" s="250" customFormat="1" spans="1:8">
-      <c r="A160" s="297"/>
-      <c r="B160" s="295" t="s">
+      <c r="A160" s="284"/>
+      <c r="B160" s="294" t="s">
         <v>13</v>
       </c>
       <c r="C160" s="283">
         <v>0.3</v>
       </c>
-      <c r="D160" s="296">
+      <c r="D160" s="295">
         <v>30000</v>
       </c>
       <c r="E160" s="265">
         <f t="shared" si="8"/>
         <v>9000</v>
       </c>
-      <c r="F160" s="300"/>
-      <c r="G160" s="300"/>
+      <c r="F160" s="289"/>
+      <c r="G160" s="289"/>
       <c r="H160" s="270"/>
     </row>
     <row r="161" s="250" customFormat="1" spans="1:7">
-      <c r="A161" s="297"/>
-      <c r="B161" s="295" t="s">
+      <c r="A161" s="284"/>
+      <c r="B161" s="294" t="s">
         <v>28</v>
       </c>
       <c r="C161" s="283">
         <v>1</v>
       </c>
-      <c r="D161" s="296">
+      <c r="D161" s="295">
         <v>49000</v>
       </c>
       <c r="E161" s="265">
         <f t="shared" si="8"/>
         <v>49000</v>
       </c>
-      <c r="F161" s="300"/>
-      <c r="G161" s="300"/>
+      <c r="F161" s="289"/>
+      <c r="G161" s="289"/>
     </row>
     <row r="162" s="250" customFormat="1" spans="1:7">
-      <c r="A162" s="297"/>
-      <c r="B162" s="295" t="s">
+      <c r="A162" s="284"/>
+      <c r="B162" s="294" t="s">
         <v>43</v>
       </c>
       <c r="C162" s="283">
         <v>4</v>
       </c>
-      <c r="D162" s="296">
+      <c r="D162" s="295">
         <v>24000</v>
       </c>
       <c r="E162" s="265">
         <f t="shared" si="8"/>
         <v>96000</v>
       </c>
-      <c r="F162" s="300"/>
-      <c r="G162" s="300"/>
+      <c r="F162" s="289"/>
+      <c r="G162" s="289"/>
     </row>
     <row r="163" s="250" customFormat="1" spans="1:7">
-      <c r="A163" s="298"/>
-      <c r="B163" s="295" t="s">
+      <c r="A163" s="285"/>
+      <c r="B163" s="294" t="s">
         <v>38</v>
       </c>
       <c r="C163" s="283">
         <v>1</v>
       </c>
-      <c r="D163" s="296">
+      <c r="D163" s="295">
         <v>19000</v>
       </c>
       <c r="E163" s="265">
         <f t="shared" si="8"/>
         <v>19000</v>
       </c>
-      <c r="F163" s="301"/>
-      <c r="G163" s="301"/>
+      <c r="F163" s="291"/>
+      <c r="G163" s="291"/>
     </row>
     <row r="164" s="250" customFormat="1" spans="1:7">
       <c r="A164" s="281">
@@ -10724,13 +10702,13 @@
       <c r="G339" s="265"/>
     </row>
     <row r="340" s="250" customFormat="1" spans="1:7">
-      <c r="A340" s="302" t="s">
+      <c r="A340" s="296" t="s">
         <v>63</v>
       </c>
-      <c r="B340" s="303"/>
-      <c r="C340" s="303"/>
-      <c r="D340" s="303"/>
-      <c r="E340" s="304"/>
+      <c r="B340" s="297"/>
+      <c r="C340" s="297"/>
+      <c r="D340" s="297"/>
+      <c r="E340" s="298"/>
       <c r="F340" s="265">
         <f>SUM(F2:F339)</f>
         <v>22634000</v>
@@ -12197,7 +12175,7 @@
       <c r="A2" s="42">
         <v>46039</v>
       </c>
-      <c r="B2" s="305" t="s">
+      <c r="B2" s="299" t="s">
         <v>136</v>
       </c>
       <c r="C2" s="44" t="s">

--- a/JANUARY 2026/BAR JANUARY 2026.xlsx
+++ b/JANUARY 2026/BAR JANUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17160" windowHeight="17020"/>
+    <workbookView windowWidth="18200" windowHeight="18640" firstSheet="10" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -332,7 +332,7 @@
     <t>MDG - F VODKA</t>
   </si>
   <si>
-    <t>SOMDG/DSP/26/01/0014</t>
+    <t>SOMDG/DSP/26/01/0104</t>
   </si>
   <si>
     <t>SO/DSP/26/01/1082</t>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
-        <v>7416000</v>
+        <v>6354000</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:3">
@@ -16630,8 +16630,8 @@
         <v>1039500</v>
       </c>
       <c r="I7" s="223">
-        <f>SUM(H7:H9)</f>
-        <v>2101500</v>
+        <f>SUM(H7)</f>
+        <v>1039500</v>
       </c>
       <c r="J7" s="230"/>
     </row>
@@ -16664,7 +16664,7 @@
         <v>1062000</v>
       </c>
       <c r="I8" s="223">
-        <f t="shared" ref="I8:I15" si="3">SUM(H8)</f>
+        <f>SUM(H8)</f>
         <v>1062000</v>
       </c>
       <c r="J8" s="230"/>
@@ -16684,11 +16684,11 @@
         <v>0</v>
       </c>
       <c r="H9" s="227">
-        <f t="shared" ref="H9:H15" si="4">SUM(D9*G9)</f>
+        <f t="shared" ref="H9:H15" si="3">SUM(D9*G9)</f>
         <v>0</v>
       </c>
       <c r="I9" s="233">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="I8:I15" si="4">SUM(H9)</f>
         <v>0</v>
       </c>
       <c r="J9" s="230"/>
@@ -16708,11 +16708,11 @@
         <v>0</v>
       </c>
       <c r="H10" s="227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="233">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J10" s="234"/>
@@ -16732,11 +16732,11 @@
         <v>0</v>
       </c>
       <c r="H11" s="227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="233">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J11" s="19"/>
@@ -16756,11 +16756,11 @@
         <v>0</v>
       </c>
       <c r="H12" s="227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="233">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J12" s="235"/>
@@ -16780,11 +16780,11 @@
         <v>0</v>
       </c>
       <c r="H13" s="227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="233">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13" s="235"/>
@@ -16804,11 +16804,11 @@
         <v>0</v>
       </c>
       <c r="H14" s="227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="233">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14" s="235"/>
@@ -16828,11 +16828,11 @@
         <v>0</v>
       </c>
       <c r="H15" s="227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="233">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15" s="235"/>
@@ -16847,7 +16847,7 @@
       <c r="E16" s="222"/>
       <c r="F16" s="229">
         <f>SUM(I2:I15)</f>
-        <v>7416000</v>
+        <v>6354000</v>
       </c>
       <c r="G16" s="229"/>
       <c r="H16" s="229"/>
